--- a/tame_output/ON/bt/strategyON_20240221.xlsx
+++ b/tame_output/ON/bt/strategyON_20240221.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-23.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.4%</t>
+          <t>447.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>22.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.3%</t>
+          <t>133.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>128.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>17.5%</t>
         </is>
       </c>
     </row>
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>1.435581050675354</v>
+        <v>1.346150090388295</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.712051774094349</v>
+        <v>3.676279389979525</v>
       </c>
       <c r="F1835" t="n">
-        <v>2.145769365459731</v>
+        <v>2.150910749934447</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.425637397413793</v>
+        <v>4.428722228098623</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>1.436294341232487</v>
+        <v>1.346863380945428</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.692162362944649</v>
+        <v>3.656389978829826</v>
       </c>
       <c r="F1836" t="n">
-        <v>2.141001271605051</v>
+        <v>2.146142656079768</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.402601813728433</v>
+        <v>4.405686644413263</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>1.442143722347731</v>
+        <v>1.352712762060672</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.694991254116621</v>
+        <v>3.659218870001798</v>
       </c>
       <c r="F1837" t="n">
-        <v>2.141001271605051</v>
+        <v>2.146142656079768</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.403090952454307</v>
+        <v>4.406175783139137</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>1.440269973802609</v>
+        <v>1.35083901351555</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.698321737320239</v>
+        <v>3.662549353205415</v>
       </c>
       <c r="F1838" t="n">
-        <v>2.139127523059929</v>
+        <v>2.144268907534645</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.4060466859489</v>
+        <v>4.40913151663373</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>1.448105235639493</v>
+        <v>1.358674275352435</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.736396926552534</v>
+        <v>3.700624542437711</v>
       </c>
       <c r="F1839" t="n">
-        <v>2.139127523059929</v>
+        <v>2.144268907534645</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.440987770446442</v>
+        <v>4.444072601131272</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>1.455777969349996</v>
+        <v>1.366347009062937</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.738043460222074</v>
+        <v>3.70227107610725</v>
       </c>
       <c r="F1840" t="n">
-        <v>2.143625142284804</v>
+        <v>2.14876652675952</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.442263782166705</v>
+        <v>4.445348612851534</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>1.461472337101355</v>
+        <v>1.372041376814297</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.719067588946354</v>
+        <v>3.683295204831531</v>
       </c>
       <c r="F1841" t="n">
-        <v>2.149319510036163</v>
+        <v>2.154460894510879</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.424426784441257</v>
+        <v>4.427511615126087</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>1.463952161153476</v>
+        <v>1.374521200866417</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.721077127697673</v>
+        <v>3.685304743582849</v>
       </c>
       <c r="F1842" t="n">
-        <v>2.149319510036163</v>
+        <v>2.154460894510879</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.425444393571728</v>
+        <v>4.428529224256557</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>1.450416677376766</v>
+        <v>1.360985717089708</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.706290966174745</v>
+        <v>3.670518582059921</v>
       </c>
       <c r="F1843" t="n">
-        <v>2.149319510036163</v>
+        <v>2.154460894510879</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.416072425559483</v>
+        <v>4.419157256244313</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>1.447678771024209</v>
+        <v>1.358247810737151</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.69527852958896</v>
+        <v>3.659506145474137</v>
       </c>
       <c r="F1844" t="n">
-        <v>2.149643390730585</v>
+        <v>2.154784775205301</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.406349479931374</v>
+        <v>4.409434310616204</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>1.451269693323989</v>
+        <v>1.36183873303693</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.701480215342574</v>
+        <v>3.665707831227751</v>
       </c>
       <c r="F1845" t="n">
-        <v>2.149643390730585</v>
+        <v>2.154784775205301</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.411114796765077</v>
+        <v>4.414199627449906</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>1.455261146119179</v>
+        <v>1.36583018583212</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.70090159257989</v>
+        <v>3.665129208465067</v>
       </c>
       <c r="F1846" t="n">
-        <v>2.153634843525775</v>
+        <v>2.158776228000491</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.411334464561431</v>
+        <v>4.414419295246261</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>1.462804141466032</v>
+        <v>1.373373181178973</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.701845682223695</v>
+        <v>3.666073298108872</v>
       </c>
       <c r="F1847" t="n">
-        <v>2.161177838872628</v>
+        <v>2.166319223347344</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.413787153274606</v>
+        <v>4.416871983959436</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>1.464783098160263</v>
+        <v>1.375352137873204</v>
       </c>
       <c r="E1848" t="n">
-        <v>3.702503481500309</v>
+        <v>3.666731097385486</v>
       </c>
       <c r="F1848" t="n">
-        <v>2.162237238834202</v>
+        <v>2.167378623308918</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.414289009850473</v>
+        <v>4.417373840535302</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>1.462592333707769</v>
+        <v>1.373161373420711</v>
       </c>
       <c r="E1849" t="n">
-        <v>3.706519320273237</v>
+        <v>3.670746936158413</v>
       </c>
       <c r="F1849" t="n">
-        <v>2.162237238834202</v>
+        <v>2.167378623308918</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.419181154404398</v>
+        <v>4.422265985089227</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>1.471893731709052</v>
+        <v>1.382462771421993</v>
       </c>
       <c r="E1850" t="n">
-        <v>3.705321335811738</v>
+        <v>3.669548951696915</v>
       </c>
       <c r="F1850" t="n">
-        <v>2.171538636835485</v>
+        <v>2.176680021310201</v>
       </c>
       <c r="G1850" t="n">
-        <v>4.419843449543156</v>
+        <v>4.422928280227985</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>1.465258809212122</v>
+        <v>1.375827848925063</v>
       </c>
       <c r="E1851" t="n">
-        <v>3.695751666119415</v>
+        <v>3.659979282004592</v>
       </c>
       <c r="F1851" t="n">
-        <v>2.164903714338555</v>
+        <v>2.170045098813271</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.408946795351447</v>
+        <v>4.412031626036276</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>1.472330992918571</v>
+        <v>1.382900032631513</v>
       </c>
       <c r="E1852" t="n">
-        <v>3.718918829340763</v>
+        <v>3.683146445225939</v>
       </c>
       <c r="F1852" t="n">
-        <v>2.171975898045004</v>
+        <v>2.17711728251972</v>
       </c>
       <c r="G1852" t="n">
-        <v>4.433528395314084</v>
+        <v>4.436613225998914</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>1.475667739427543</v>
+        <v>1.386236779140484</v>
       </c>
       <c r="E1853" t="n">
-        <v>3.72835227835292</v>
+        <v>3.692579894238097</v>
       </c>
       <c r="F1853" t="n">
-        <v>2.174667930464036</v>
+        <v>2.179809314938752</v>
       </c>
       <c r="G1853" t="n">
-        <v>4.443242365174072</v>
+        <v>4.446327195858902</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>1.474215072964433</v>
+        <v>1.384784112677375</v>
       </c>
       <c r="E1854" t="n">
-        <v>3.728877603811409</v>
+        <v>3.693105219696585</v>
       </c>
       <c r="F1854" t="n">
-        <v>2.173215264000926</v>
+        <v>2.178356648475642</v>
       </c>
       <c r="G1854" t="n">
-        <v>4.443477157339939</v>
+        <v>4.446561988024769</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>1.473784373915838</v>
+        <v>1.38435341362878</v>
       </c>
       <c r="E1855" t="n">
-        <v>3.727247863004834</v>
+        <v>3.69147547889001</v>
       </c>
       <c r="F1855" t="n">
-        <v>2.173215264000926</v>
+        <v>2.178356648475642</v>
       </c>
       <c r="G1855" t="n">
-        <v>4.442019696152802</v>
+        <v>4.445104526837632</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>1.472947196934003</v>
+        <v>1.383516236646944</v>
       </c>
       <c r="E1856" t="n">
-        <v>3.728682115666716</v>
+        <v>3.692909731551893</v>
       </c>
       <c r="F1856" t="n">
-        <v>2.172261012739055</v>
+        <v>2.177402397213771</v>
       </c>
       <c r="G1856" t="n">
-        <v>4.443216268850295</v>
+        <v>4.446301099535125</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>1.461442711935718</v>
+        <v>1.372011751648659</v>
       </c>
       <c r="E1857" t="n">
-        <v>3.72018638032366</v>
+        <v>3.684413996208836</v>
       </c>
       <c r="F1857" t="n">
-        <v>2.16075652774077</v>
+        <v>2.165897912215486</v>
       </c>
       <c r="G1857" t="n">
-        <v>4.432419636507582</v>
+        <v>4.435504467192412</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>1.45478177171357</v>
+        <v>1.365350811426512</v>
       </c>
       <c r="E1858" t="n">
-        <v>3.71929493093506</v>
+        <v>3.683522546820237</v>
       </c>
       <c r="F1858" t="n">
-        <v>2.16075652774077</v>
+        <v>2.165897912215486</v>
       </c>
       <c r="G1858" t="n">
-        <v>4.434192563207842</v>
+        <v>4.437277393892671</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>1.452631251933359</v>
+        <v>1.3632002916463</v>
       </c>
       <c r="E1859" t="n">
-        <v>3.70476761049038</v>
+        <v>3.668995226375557</v>
       </c>
       <c r="F1859" t="n">
-        <v>2.159108519902172</v>
+        <v>2.164249904376888</v>
       </c>
       <c r="G1859" t="n">
-        <v>4.419536645972087</v>
+        <v>4.422621476656917</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>1.465693506282326</v>
+        <v>1.376262545995268</v>
       </c>
       <c r="E1860" t="n">
-        <v>3.698277287232058</v>
+        <v>3.662504903117235</v>
       </c>
       <c r="F1860" t="n">
-        <v>2.164943066692238</v>
+        <v>2.170084451166954</v>
       </c>
       <c r="G1860" t="n">
-        <v>4.411322149048218</v>
+        <v>4.414406979733047</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>1.464129355172023</v>
+        <v>1.374698394884965</v>
       </c>
       <c r="E1861" t="n">
-        <v>3.696232218443902</v>
+        <v>3.660459834329078</v>
       </c>
       <c r="F1861" t="n">
-        <v>2.164943066692238</v>
+        <v>2.170084451166954</v>
       </c>
       <c r="G1861" t="n">
-        <v>4.409902740704183</v>
+        <v>4.412987571389012</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>1.466177940033734</v>
+        <v>1.376746979746676</v>
       </c>
       <c r="E1862" t="n">
-        <v>3.703539212622827</v>
+        <v>3.667766828508004</v>
       </c>
       <c r="F1862" t="n">
-        <v>2.16719076675043</v>
+        <v>2.172332151225147</v>
       </c>
       <c r="G1862" t="n">
-        <v>4.41773892097334</v>
+        <v>4.420823751658169</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>1.468605004562452</v>
+        <v>1.379174044275394</v>
       </c>
       <c r="E1863" t="n">
-        <v>3.703764553440146</v>
+        <v>3.667992169325323</v>
       </c>
       <c r="F1863" t="n">
-        <v>2.166857984943279</v>
+        <v>2.171999369417995</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.41679376689488</v>
+        <v>4.41987859757971</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>1.467312982788114</v>
+        <v>1.377882022501056</v>
       </c>
       <c r="E1864" t="n">
-        <v>3.70200928874517</v>
+        <v>3.666236904630347</v>
       </c>
       <c r="F1864" t="n">
-        <v>2.165565963168941</v>
+        <v>2.170707347643657</v>
       </c>
       <c r="G1864" t="n">
-        <v>4.414780097845036</v>
+        <v>4.417864928529866</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>1.462498390533273</v>
+        <v>1.373067430246214</v>
       </c>
       <c r="E1865" t="n">
-        <v>3.695268884314694</v>
+        <v>3.659496500199871</v>
       </c>
       <c r="F1865" t="n">
-        <v>2.165565963168941</v>
+        <v>2.170707347643657</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.409965530316497</v>
+        <v>4.413050361001327</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>1.465655091563477</v>
+        <v>1.376224131276419</v>
       </c>
       <c r="E1866" t="n">
-        <v>3.694525615335653</v>
+        <v>3.65875323122083</v>
       </c>
       <c r="F1866" t="n">
-        <v>2.165565963168941</v>
+        <v>2.170707347643657</v>
       </c>
       <c r="G1866" t="n">
-        <v>4.407959580925374</v>
+        <v>4.411044411610204</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>1.461642059150955</v>
+        <v>1.372211098863897</v>
       </c>
       <c r="E1867" t="n">
-        <v>3.703179093039323</v>
+        <v>3.6674067089245</v>
       </c>
       <c r="F1867" t="n">
-        <v>2.165565963168941</v>
+        <v>2.170707347643657</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.418218271594053</v>
+        <v>4.421303102278883</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>1.447927194825844</v>
+        <v>1.358496234538785</v>
       </c>
       <c r="E1868" t="n">
-        <v>3.693792712454974</v>
+        <v>3.658020328340151</v>
       </c>
       <c r="F1868" t="n">
-        <v>2.165565963168941</v>
+        <v>2.170707347643657</v>
       </c>
       <c r="G1868" t="n">
-        <v>4.414317836739748</v>
+        <v>4.417402667424578</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>1.442410274981877</v>
+        <v>1.352979314694819</v>
       </c>
       <c r="E1869" t="n">
-        <v>3.689990864572389</v>
+        <v>3.654218480457565</v>
       </c>
       <c r="F1869" t="n">
-        <v>2.165565963168941</v>
+        <v>2.170707347643657</v>
       </c>
       <c r="G1869" t="n">
-        <v>4.412722756794749</v>
+        <v>4.415807587479579</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>1.437597236516541</v>
+        <v>1.348166276229482</v>
       </c>
       <c r="E1870" t="n">
-        <v>3.691844625115462</v>
+        <v>3.656072241000639</v>
       </c>
       <c r="F1870" t="n">
-        <v>2.164019328466155</v>
+        <v>2.169160712940871</v>
       </c>
       <c r="G1870" t="n">
-        <v>4.415573751902286</v>
+        <v>4.418658582587116</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>1.439714395240834</v>
+        <v>1.350283434953775</v>
       </c>
       <c r="E1871" t="n">
-        <v>3.688665184070776</v>
+        <v>3.652892799955953</v>
       </c>
       <c r="F1871" t="n">
-        <v>2.164019328466155</v>
+        <v>2.169160712940871</v>
       </c>
       <c r="G1871" t="n">
-        <v>4.411547447367883</v>
+        <v>4.414632278052713</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>1.440191741819323</v>
+        <v>1.350760781532265</v>
       </c>
       <c r="E1872" t="n">
-        <v>3.688754021380588</v>
+        <v>3.652981637265765</v>
       </c>
       <c r="F1872" t="n">
-        <v>2.164019328466155</v>
+        <v>2.169160712940871</v>
       </c>
       <c r="G1872" t="n">
-        <v>4.411445346046299</v>
+        <v>4.414530176731128</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>1.441216528126181</v>
+        <v>1.351785567839122</v>
       </c>
       <c r="E1873" t="n">
-        <v>3.691735451874761</v>
+        <v>3.655963067759938</v>
       </c>
       <c r="F1873" t="n">
-        <v>2.165044114773012</v>
+        <v>2.170185499247729</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.414631733801843</v>
+        <v>4.417716564486673</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>1.422475147867262</v>
+        <v>1.333044187580204</v>
       </c>
       <c r="E1874" t="n">
-        <v>3.689589203069244</v>
+        <v>3.65381681895442</v>
       </c>
       <c r="F1874" t="n">
-        <v>2.165044114773012</v>
+        <v>2.170185499247729</v>
       </c>
       <c r="G1874" t="n">
-        <v>4.419982037099894</v>
+        <v>4.423066867784724</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>1.409505805082164</v>
+        <v>1.320074844795105</v>
       </c>
       <c r="E1875" t="n">
-        <v>3.692317485912382</v>
+        <v>3.656545101797558</v>
       </c>
       <c r="F1875" t="n">
-        <v>2.152074771987914</v>
+        <v>2.15721615646263</v>
       </c>
       <c r="G1875" t="n">
-        <v>4.420116451386012</v>
+        <v>4.423201282070842</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>1.415981951875723</v>
+        <v>1.326550991588665</v>
       </c>
       <c r="E1876" t="n">
-        <v>3.697949695251574</v>
+        <v>3.662177311136751</v>
       </c>
       <c r="F1876" t="n">
-        <v>2.158550918781474</v>
+        <v>2.16369230325619</v>
       </c>
       <c r="G1876" t="n">
-        <v>4.427043890083917</v>
+        <v>4.430128720768747</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>1.419672876832135</v>
+        <v>1.330241916545076</v>
       </c>
       <c r="E1877" t="n">
-        <v>3.699426065234139</v>
+        <v>3.663653681119316</v>
       </c>
       <c r="F1877" t="n">
-        <v>2.158550918781474</v>
+        <v>2.16369230325619</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.427043890083917</v>
+        <v>4.430128720768747</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>1.42688822970395</v>
+        <v>1.337457269416892</v>
       </c>
       <c r="E1878" t="n">
-        <v>3.707825403501507</v>
+        <v>3.672053019386684</v>
       </c>
       <c r="F1878" t="n">
-        <v>2.228329154071855</v>
+        <v>2.233470538546571</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.474424028376788</v>
+        <v>4.477508859061618</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>1.477916075785776</v>
+        <v>1.388485115498718</v>
       </c>
       <c r="E1879" t="n">
-        <v>3.732719096418674</v>
+        <v>3.696946712303851</v>
       </c>
       <c r="F1879" t="n">
-        <v>2.303538492378956</v>
+        <v>2.308679876853672</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.524032185845485</v>
+        <v>4.527117016530315</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.349268194805817</v>
+        <v>3.345854276523589</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>1.545959417185972</v>
+        <v>1.543521688634322</v>
       </c>
       <c r="E1880" t="n">
-        <v>3.775308134472174</v>
+        <v>3.774333043051513</v>
       </c>
       <c r="F1880" t="n">
-        <v>2.371581833779152</v>
+        <v>2.463716449989276</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.580229892179023</v>
+        <v>4.635510661905098</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240221.xlsx
+++ b/tame_output/ON/bt/strategyON_20240221.xlsx
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>1.543521688634322</v>
+        <v>1.543573048142796</v>
       </c>
       <c r="E1880" t="n">
-        <v>3.774333043051513</v>
+        <v>3.774353586854903</v>
       </c>
       <c r="F1880" t="n">
-        <v>2.463716449989276</v>
+        <v>2.463767809497751</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.635510661905098</v>
+        <v>4.635541477610182</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240221.xlsx
+++ b/tame_output/ON/bt/strategyON_20240221.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>447.6%</t>
+          <t>448.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>-2.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.6%</t>
+          <t>131.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>128.3%</t>
+          <t>125.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>1.543573048142796</v>
+        <v>1.461954947166166</v>
       </c>
       <c r="E1880" t="n">
-        <v>3.774353586854903</v>
+        <v>3.741706346464251</v>
       </c>
       <c r="F1880" t="n">
-        <v>2.463767809497751</v>
+        <v>2.382149708521121</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.635541477610182</v>
+        <v>4.586570617024205</v>
       </c>
     </row>
   </sheetData>
